--- a/dados/excel/folha_mensal_recorrente.xlsx
+++ b/dados/excel/folha_mensal_recorrente.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Série temporal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,22 +127,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -661,17 +661,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>﻿ano</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Número decimal (#,##0,00)</t>
+          <t>Número inteiro (#,##0)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -807,7 +807,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>﻿ano</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -845,1292 +845,1315 @@
       <c r="A2" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="9" t="n">
         <v>39388760.17</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="9" t="n">
         <v>25884140.51</v>
       </c>
-      <c r="E2" s="8" t="n">
-        <v>10965</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>10965</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>3592.23</v>
+      <c r="E2" s="10" t="n">
+        <v>10897</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>10897</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>3614.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="12" t="n">
         <v>54775880.48</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="12" t="n">
         <v>34514444.45</v>
       </c>
-      <c r="E3" s="11" t="n">
-        <v>9663</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>9663</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>5668.62</v>
+      <c r="E3" s="13" t="n">
+        <v>9560</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>9560</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>5729.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>63473301.38</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>42578222.59</v>
       </c>
-      <c r="E4" s="8" t="n">
-        <v>11279</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>11279</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>5627.56</v>
+      <c r="E4" s="10" t="n">
+        <v>11216</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>11216</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>5659.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>67959523.12</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="12" t="n">
         <v>43166143.88</v>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>11503</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>11503</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>5907.98</v>
+      <c r="E5" s="13" t="n">
+        <v>11452</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>11452</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>5934.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>70049213.92</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>45268318.56</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>11668</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>11668</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>6003.53</v>
+      <c r="E6" s="10" t="n">
+        <v>11600</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>11600</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>6038.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="12" t="n">
         <v>70296141.45</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>45474814.89</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>11858</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>11858</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>5928.16</v>
+      <c r="E7" s="13" t="n">
+        <v>11790</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>11790</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>5962.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <v>67967446.73</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>44345983.31</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>11702</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>11702</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>5808.19</v>
+      <c r="E8" s="10" t="n">
+        <v>11611</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>11611</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>5853.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="12" t="n">
         <v>68353597.40000001</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>43921219.27</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>11769</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>11769</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>5807.94</v>
+      <c r="E9" s="13" t="n">
+        <v>11663</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>11663</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>5860.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>70981843.95999999</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>46120078.4</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>11979</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>11979</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>5925.52</v>
+      <c r="E10" s="10" t="n">
+        <v>11894</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>11894</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>5967.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="12" t="n">
         <v>72983925.44</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <v>46151426.79</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>11856</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>11856</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>6155.86</v>
+      <c r="E11" s="13" t="n">
+        <v>11806</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>11806</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>6181.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>99160417.78</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>73272778.22</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>11844</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>11844</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>8372.209999999999</v>
+      <c r="E12" s="10" t="n">
+        <v>11798</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>11798</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>8404.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="12" t="n">
         <v>70379347.7</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>45787052.68</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>11447</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>11447</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>6148.28</v>
+      <c r="E13" s="13" t="n">
+        <v>11399</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>11399</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>6174.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <v>46113178.03</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>30798625.9</v>
       </c>
-      <c r="E14" s="8" t="n">
-        <v>10955</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>10955</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>4209.33</v>
+      <c r="E14" s="10" t="n">
+        <v>8225</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>8225</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>5606.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="12" t="n">
         <v>77481510.97</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="12" t="n">
         <v>48515810.27</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>10130</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>10130</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>7648.72</v>
+      <c r="E15" s="13" t="n">
+        <v>9959</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>9959</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>7780.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <v>85811786.53</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>56153884.5</v>
       </c>
-      <c r="E16" s="8" t="n">
-        <v>11661</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>11661</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>7358.87</v>
+      <c r="E16" s="10" t="n">
+        <v>11549</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>11549</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>7430.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="12" t="n">
         <v>75511775.65000001</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="12" t="n">
         <v>48059194.03</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>12356</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>12356</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>6111.34</v>
+      <c r="E17" s="13" t="n">
+        <v>12269</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>12269</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>6154.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="9" t="n">
         <v>75200151.97</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>48040952.7</v>
       </c>
-      <c r="E18" s="8" t="n">
-        <v>12384</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>12384</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>6072.36</v>
+      <c r="E18" s="10" t="n">
+        <v>12296</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>12296</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>6115.82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="12" t="n">
         <v>78547301.2</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <v>50509580.76</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>12628</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>12628</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>6220.09</v>
+      <c r="E19" s="13" t="n">
+        <v>12553</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>12553</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>6257.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="9" t="n">
         <v>79328361.48999999</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>51490923.44</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>12490</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>12490</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>6351.35</v>
+      <c r="E20" s="10" t="n">
+        <v>12421</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>12421</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>6386.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="12" t="n">
         <v>84120310.25</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="12" t="n">
         <v>55160945.34</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>12378</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>12378</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>6795.95</v>
+      <c r="E21" s="13" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>12300</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>6839.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="9" t="n">
         <v>85158075.52</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="9" t="n">
         <v>55877051.83</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>12635</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>12635</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>6739.86</v>
+      <c r="E22" s="10" t="n">
+        <v>12573</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>12573</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>6773.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="12" t="n">
         <v>84261902.01000001</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="12" t="n">
         <v>55391262.47</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>12580</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>12580</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>6698.08</v>
+      <c r="E23" s="13" t="n">
+        <v>12507</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>12507</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>6737.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="9" t="n">
         <v>112349507.35</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>83742702.68000001</v>
       </c>
-      <c r="E24" s="8" t="n">
-        <v>12592</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>12592</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>8922.290000000001</v>
+      <c r="E24" s="10" t="n">
+        <v>12544</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>12544</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>8956.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="12" t="n">
         <v>85570759.92</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>54715125.67</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>12210</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>12210</v>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>7008.25</v>
+      <c r="E25" s="13" t="n">
+        <v>12160</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>12160</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>7037.07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="9" t="n">
         <v>54534527.82</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="9" t="n">
         <v>36431554.02</v>
       </c>
-      <c r="E26" s="8" t="n">
-        <v>11834</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>11834</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>4608.29</v>
+      <c r="E26" s="10" t="n">
+        <v>9986</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>9986</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>5461.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="12" t="n">
         <v>81725640.14</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="12" t="n">
         <v>53301214.96</v>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>10837</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>10837</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>7541.35</v>
+      <c r="E27" s="13" t="n">
+        <v>10739</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>10739</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>7610.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="9" t="n">
         <v>104122520.64</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="9" t="n">
         <v>70653369.02</v>
       </c>
-      <c r="E28" s="8" t="n">
-        <v>12311</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>12311</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>8457.68</v>
+      <c r="E28" s="10" t="n">
+        <v>12223</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>12223</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>8518.57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="12" t="n">
         <v>91253635.37</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="12" t="n">
         <v>60649631.74</v>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>12849</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>12849</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>7102</v>
+      <c r="E29" s="13" t="n">
+        <v>12787</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>12787</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>7136.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="9" t="n">
         <v>92663211.54000001</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="9" t="n">
         <v>61222582.45</v>
       </c>
-      <c r="E30" s="8" t="n">
-        <v>13046</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>13046</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>7102.81</v>
+      <c r="E30" s="10" t="n">
+        <v>12962</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>12962</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>7148.84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="12" t="n">
         <v>92181012.79000001</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="12" t="n">
         <v>61259451.01</v>
       </c>
-      <c r="E31" s="11" t="n">
-        <v>13078</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>13078</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>7048.56</v>
+      <c r="E31" s="13" t="n">
+        <v>13017</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>13017</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>7081.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="9" t="n">
         <v>90898983.33</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="9" t="n">
         <v>60693122.28</v>
       </c>
-      <c r="E32" s="8" t="n">
-        <v>13071</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>13071</v>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>6954.25</v>
+      <c r="E32" s="10" t="n">
+        <v>13009</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>13009</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>6987.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="12" t="n">
         <v>89691798.92</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="12" t="n">
         <v>59049484.1</v>
       </c>
-      <c r="E33" s="11" t="n">
-        <v>12710</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>12710</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>7056.79</v>
+      <c r="E33" s="13" t="n">
+        <v>12652</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>12652</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>7089.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C34" s="9" t="n">
         <v>93066910.95999999</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="9" t="n">
         <v>62008719.48</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>13162</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>13162</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>7070.88</v>
+      <c r="E34" s="10" t="n">
+        <v>13103</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>13103</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>7102.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="12" t="n">
         <v>93637538.51000001</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="12" t="n">
         <v>61993770.78</v>
       </c>
-      <c r="E35" s="11" t="n">
-        <v>13230</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>13230</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>7077.67</v>
+      <c r="E35" s="13" t="n">
+        <v>13180</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>13180</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>7104.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C36" s="9" t="n">
         <v>126570026.17</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="9" t="n">
         <v>61545324.5</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>13102</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>13102</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>9660.360000000001</v>
+      <c r="E36" s="10" t="n">
+        <v>13053</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>13053</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>9696.620000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="12" t="n">
         <v>90718642.77</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="12" t="n">
         <v>60103782.75</v>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>12881</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>12881</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>7042.83</v>
+      <c r="E37" s="13" t="n">
+        <v>12825</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>12825</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>7073.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="9" t="n">
         <v>62470835.19</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="9" t="n">
         <v>43347702.48</v>
       </c>
-      <c r="E38" s="8" t="n">
-        <v>12432</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>12432</v>
-      </c>
-      <c r="G38" s="10" t="n">
-        <v>5025</v>
+      <c r="E38" s="10" t="n">
+        <v>12317</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>12317</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>5071.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="13" t="n">
+      <c r="C39" s="12" t="n">
         <v>91432204.45999999</v>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="12" t="n">
         <v>59111963.19</v>
       </c>
-      <c r="E39" s="11" t="n">
-        <v>10886</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>10886</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>8399.059999999999</v>
+      <c r="E39" s="13" t="n">
+        <v>10814</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>10814</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>8454.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C40" s="9" t="n">
         <v>111171135.9</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="9" t="n">
         <v>70649522.98</v>
       </c>
-      <c r="E40" s="8" t="n">
-        <v>13342</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>13342</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>8332.42</v>
+      <c r="E40" s="10" t="n">
+        <v>13258</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>13258</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>8385.209999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="13" t="n">
+      <c r="C41" s="12" t="n">
         <v>101323425.97</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="12" t="n">
         <v>66032306.49</v>
       </c>
-      <c r="E41" s="11" t="n">
-        <v>12981</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>12981</v>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>7805.52</v>
+      <c r="E41" s="13" t="n">
+        <v>12924</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>12924</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>7839.94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="9" t="n">
         <v>101908112.76</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="9" t="n">
         <v>66526892.91</v>
       </c>
-      <c r="E42" s="8" t="n">
-        <v>13199</v>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>13199</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>7720.9</v>
+      <c r="E42" s="10" t="n">
+        <v>13157</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>13157</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>7745.54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="12" t="n">
         <v>107613320.94</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="12" t="n">
         <v>69858350.84999999</v>
       </c>
-      <c r="E43" s="11" t="n">
-        <v>13335</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>13335</v>
-      </c>
-      <c r="G43" s="13" t="n">
-        <v>8069.99</v>
+      <c r="E43" s="13" t="n">
+        <v>13295</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>13295</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>8094.27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="9" t="n">
         <v>102714470.83</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="9" t="n">
         <v>67279213.34</v>
       </c>
-      <c r="E44" s="8" t="n">
-        <v>13359</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>13359</v>
-      </c>
-      <c r="G44" s="10" t="n">
-        <v>7688.78</v>
+      <c r="E44" s="10" t="n">
+        <v>13302</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>13302</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>7721.73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C45" s="13" t="n">
+      <c r="C45" s="12" t="n">
         <v>104203860.6</v>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="12" t="n">
         <v>67543430.70999999</v>
       </c>
-      <c r="E45" s="11" t="n">
-        <v>13013</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>13013</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>8007.67</v>
+      <c r="E45" s="13" t="n">
+        <v>12944</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>12944</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>8050.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="9" t="n">
         <v>105644747.89</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="9" t="n">
         <v>68831600.47</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>13497</v>
-      </c>
-      <c r="F46" s="8" t="n">
-        <v>13497</v>
-      </c>
-      <c r="G46" s="10" t="n">
-        <v>7827.28</v>
+      <c r="E46" s="10" t="n">
+        <v>13436</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>13436</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>7862.81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C47" s="13" t="n">
+      <c r="C47" s="12" t="n">
         <v>104674386.11</v>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="12" t="n">
         <v>67799732.73999999</v>
       </c>
-      <c r="E47" s="11" t="n">
-        <v>13616</v>
-      </c>
-      <c r="F47" s="11" t="n">
-        <v>13616</v>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>7687.6</v>
+      <c r="E47" s="13" t="n">
+        <v>13597</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>13597</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>7698.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="9" t="n">
         <v>142324658.24</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="9" t="n">
         <v>105085425.77</v>
       </c>
-      <c r="E48" s="8" t="n">
-        <v>13511</v>
-      </c>
-      <c r="F48" s="8" t="n">
-        <v>13511</v>
-      </c>
-      <c r="G48" s="10" t="n">
-        <v>10533.98</v>
+      <c r="E48" s="10" t="n">
+        <v>13487</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>13487</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>10552.73</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C49" s="13" t="n">
+      <c r="C49" s="12" t="n">
         <v>103506753.24</v>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="12" t="n">
         <v>66727535.85</v>
       </c>
-      <c r="E49" s="11" t="n">
-        <v>13346</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>13346</v>
-      </c>
-      <c r="G49" s="13" t="n">
-        <v>7755.64</v>
+      <c r="E49" s="13" t="n">
+        <v>13283</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>13283</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>7792.42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="9" t="n">
         <v>73110023.62</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="9" t="n">
         <v>51418744.55</v>
       </c>
-      <c r="E50" s="8" t="n">
-        <v>12868</v>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>12868</v>
-      </c>
-      <c r="G50" s="10" t="n">
-        <v>5681.54</v>
+      <c r="E50" s="10" t="n">
+        <v>12843</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>12843</v>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>5692.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="13" t="n">
+      <c r="C51" s="12" t="n">
         <v>95759088.05</v>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="12" t="n">
         <v>61926120.66</v>
       </c>
-      <c r="E51" s="11" t="n">
-        <v>10817</v>
-      </c>
-      <c r="F51" s="11" t="n">
-        <v>10817</v>
-      </c>
-      <c r="G51" s="13" t="n">
-        <v>8852.65</v>
+      <c r="E51" s="13" t="n">
+        <v>10785</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>10785</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>8878.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B52" s="9" t="n">
+      <c r="B52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="9" t="n">
         <v>123763008.25</v>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="9" t="n">
         <v>83468979.23</v>
       </c>
-      <c r="E52" s="8" t="n">
-        <v>13483</v>
-      </c>
-      <c r="F52" s="8" t="n">
-        <v>13483</v>
-      </c>
-      <c r="G52" s="10" t="n">
-        <v>9179.190000000001</v>
+      <c r="E52" s="10" t="n">
+        <v>13439</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>13439</v>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>9209.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C53" s="13" t="n">
+      <c r="C53" s="12" t="n">
         <v>110616293.03</v>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="12" t="n">
         <v>72467124.92</v>
       </c>
-      <c r="E53" s="11" t="n">
-        <v>13521</v>
-      </c>
-      <c r="F53" s="11" t="n">
-        <v>13521</v>
-      </c>
-      <c r="G53" s="13" t="n">
-        <v>8181.07</v>
+      <c r="E53" s="13" t="n">
+        <v>13490</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>13490</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>8199.870000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C54" s="10" t="n">
+      <c r="C54" s="9" t="n">
         <v>113130737.28</v>
       </c>
-      <c r="D54" s="10" t="n">
+      <c r="D54" s="9" t="n">
         <v>73566150.59999999</v>
       </c>
-      <c r="E54" s="8" t="n">
-        <v>13497</v>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>13497</v>
-      </c>
-      <c r="G54" s="10" t="n">
-        <v>8381.92</v>
+      <c r="E54" s="10" t="n">
+        <v>13473</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>13473</v>
+      </c>
+      <c r="G54" s="9" t="n">
+        <v>8396.85</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C55" s="13" t="n">
+      <c r="C55" s="12" t="n">
         <v>116997557.31</v>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="12" t="n">
         <v>76124846.59999999</v>
       </c>
-      <c r="E55" s="11" t="n">
-        <v>13812</v>
-      </c>
-      <c r="F55" s="11" t="n">
-        <v>13812</v>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>8470.719999999999</v>
+      <c r="E55" s="13" t="n">
+        <v>13789</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>13789</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>8484.85</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B56" s="9" t="n">
+      <c r="B56" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C56" s="9" t="n">
         <v>121748838.55</v>
       </c>
-      <c r="D56" s="10" t="n">
+      <c r="D56" s="9" t="n">
         <v>72937410.25</v>
       </c>
-      <c r="E56" s="8" t="n">
-        <v>13835</v>
-      </c>
-      <c r="F56" s="8" t="n">
-        <v>13835</v>
-      </c>
-      <c r="G56" s="10" t="n">
-        <v>8800.059999999999</v>
+      <c r="E56" s="10" t="n">
+        <v>13813</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>13813</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>8814.08</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C57" s="13" t="n">
+      <c r="C57" s="12" t="n">
         <v>117432210.51</v>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="12" t="n">
         <v>75865571.67</v>
       </c>
-      <c r="E57" s="11" t="n">
-        <v>13845</v>
-      </c>
-      <c r="F57" s="11" t="n">
-        <v>13845</v>
-      </c>
-      <c r="G57" s="13" t="n">
-        <v>8481.92</v>
+      <c r="E57" s="13" t="n">
+        <v>13829</v>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>13829</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>8491.74</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>121280800.77</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>79208425.69</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>14368</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>14368</v>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>8441.040000000001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G57"/>
+  <autoFilter ref="A1:G58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2141,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2170,7 +2193,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="B4" s="15" t="n">
@@ -2180,7 +2203,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2/2022</t>
         </is>
       </c>
       <c r="B5" s="15" t="n">
@@ -2190,7 +2213,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="B6" s="15" t="n">
@@ -2200,7 +2223,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
@@ -2210,7 +2233,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>5/2022</t>
         </is>
       </c>
       <c r="B8" s="15" t="n">
@@ -2220,7 +2243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="B9" s="15" t="n">
@@ -2230,7 +2253,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>7/2022</t>
         </is>
       </c>
       <c r="B10" s="15" t="n">
@@ -2240,7 +2263,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="B11" s="15" t="n">
@@ -2250,7 +2273,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="B12" s="15" t="n">
@@ -2260,7 +2283,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B13" s="15" t="n">
@@ -2270,7 +2293,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -2280,7 +2303,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -2290,7 +2313,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -2300,7 +2323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -2310,7 +2333,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>3/2023</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -2320,7 +2343,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -2330,7 +2353,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>5/2023</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -2340,7 +2363,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>6/2023</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -2350,7 +2373,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>7/2023</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -2360,7 +2383,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>8/2023</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -2370,7 +2393,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>9/2023</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -2380,7 +2403,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -2390,7 +2413,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -2400,7 +2423,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -2410,7 +2433,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -2420,7 +2443,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -2430,7 +2453,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
@@ -2440,7 +2463,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="B31" s="15" t="n">
@@ -2450,7 +2473,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="B32" s="15" t="n">
@@ -2460,7 +2483,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>6/2024</t>
         </is>
       </c>
       <c r="B33" s="15" t="n">
@@ -2470,7 +2493,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>7/2024</t>
         </is>
       </c>
       <c r="B34" s="15" t="n">
@@ -2480,7 +2503,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>8/2024</t>
         </is>
       </c>
       <c r="B35" s="15" t="n">
@@ -2490,7 +2513,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>9/2024</t>
         </is>
       </c>
       <c r="B36" s="15" t="n">
@@ -2500,7 +2523,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B37" s="15" t="n">
@@ -2510,7 +2533,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B38" s="15" t="n">
@@ -2520,7 +2543,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B39" s="15" t="n">
@@ -2530,7 +2553,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1/2025</t>
         </is>
       </c>
       <c r="B40" s="15" t="n">
@@ -2540,7 +2563,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2/2025</t>
         </is>
       </c>
       <c r="B41" s="15" t="n">
@@ -2550,7 +2573,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>3/2025</t>
         </is>
       </c>
       <c r="B42" s="15" t="n">
@@ -2560,7 +2583,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>4/2025</t>
         </is>
       </c>
       <c r="B43" s="15" t="n">
@@ -2570,7 +2593,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>5/2025</t>
         </is>
       </c>
       <c r="B44" s="15" t="n">
@@ -2580,7 +2603,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="B45" s="15" t="n">
@@ -2590,7 +2613,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="B46" s="15" t="n">
@@ -2600,7 +2623,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>8/2025</t>
         </is>
       </c>
       <c r="B47" s="15" t="n">
@@ -2610,7 +2633,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>9/2025</t>
         </is>
       </c>
       <c r="B48" s="15" t="n">
@@ -2620,7 +2643,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B49" s="15" t="n">
@@ -2630,7 +2653,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B50" s="15" t="n">
@@ -2640,7 +2663,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>12/2025</t>
         </is>
       </c>
       <c r="B51" s="15" t="n">
@@ -2650,7 +2673,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="B52" s="15" t="n">
@@ -2660,7 +2683,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2/2026</t>
         </is>
       </c>
       <c r="B53" s="15" t="n">
@@ -2670,7 +2693,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>3/2026</t>
         </is>
       </c>
       <c r="B54" s="15" t="n">
@@ -2680,7 +2703,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4/2026</t>
         </is>
       </c>
       <c r="B55" s="15" t="n">
@@ -2690,7 +2713,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="B56" s="15" t="n">
@@ -2700,7 +2723,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>6/2026</t>
         </is>
       </c>
       <c r="B57" s="15" t="n">
@@ -2710,7 +2733,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>7/2026</t>
         </is>
       </c>
       <c r="B58" s="15" t="n">
@@ -2720,11 +2743,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>8/2026</t>
         </is>
       </c>
       <c r="B59" s="15" t="n">
         <v>117432210.51</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="n">
+        <v>121280800.77</v>
       </c>
     </row>
   </sheetData>
